--- a/SLR/Full-Paper-Read/Paper-Review/PS12.xlsx
+++ b/SLR/Full-Paper-Read/Paper-Review/PS12.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="63">
   <si>
     <t>ID</t>
   </si>
@@ -26,81 +26,109 @@
     <t>The paper proposes the following contributions:</t>
   </si>
   <si>
-    <t>The paper outlines essential standardization activities, real-time Big Data processing approaches, and necessary analytical tools, emphasizing that IoT's evolution relies on collaboration between standardization organizations, open-source communities, and IT experts.
-Verifying data and metadata, including their provenance and sensor locations, poses additional challenges, necessitating detailed modeling of these interconnected elements.
-Effective business integration requires both vertical integration of technical and business processes and horizontal integration across company boundaries, encompassing the entire value chain.
-IoT and Big Data technologies originate from distinct backgrounds. IoT is primarily hardware-driven, while Big Data has roots in software paradigms developed by internet and social media giants like Google, Facebook, and Yahoo. Both hardware and software are integral to enabling data-driven IoT solutions. The paper addresses software concepts and platforms essential for managing large-scale IoT data, highlighting the need for robust analytical tools to unlock deeper data value.
-IoT offers significant opportunities, supported by the open-source Hadoop ecosystem, accepted exchange formats, and expanding standards. This convergence of platforms suggests a future where IoT seamlessly integrates into various aspects of life, driven by continuous innovation and standardization.</t>
-  </si>
-  <si>
-    <t>User requirements
-Data sovereignty The data owner specifies the terms and conditions of use for data
-Decentral data management Data management remains with the data owner, if desired
-Data economy Data is viewed as an economic asset. It can be distinguished into three categories: private data, i.e., data
-belonging to a specific value creation chain, which is available to selected companies only, and public data
-(weather or traffic information, geo data etc.)
-Value creation The IDS facilitates the creation and use of smart services and digital business models
-Easy linkage of data Linked-data concepts and common vocabularies facilitate the integration of data between participants
-Trust All participants, data sources, and data services of the IDS are certified against commonly defined rules
-Secure data supply chain Data exchange is secure across the entire data supply chain, i.e. from data creation to data capture to data usage
-Data governance Participants jointly decide on data management processes as well as on applicable rights and dutie</t>
+    <t>This paper presents an industrial case study on the application of the Arrowhead framework. The framework is implemented in the Machine Tooling ecosystem and enables the integration of grinding machines with other sensors, components or machines. Different software engineering tools offered with Arrowhead are used to design new solutions in Cyber-Physical System and Internet of Things in Industry 4.0 and make them Arrowhead compliant, for fast deployment of platforms and applications (Dockers) or for testing purposes (Management tool).</t>
+  </si>
+  <si>
+    <t>&lt;add your comment here if any&gt;</t>
   </si>
   <si>
     <t>CPS Case Study / Example availability</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <i/>
+        <color rgb="FF1155CC"/>
+        <sz val="10.0"/>
+        <u/>
+      </rPr>
+      <t>https://productive40.eu/</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <i/>
+        <color rgb="FF000000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t xml:space="preserve"> not accessible</t>
+    </r>
+  </si>
+  <si>
+    <t>SECO Tools Availability (add repository or website in the comment)</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <i/>
+        <color rgb="FF1155CC"/>
+        <sz val="10.0"/>
+        <u/>
+      </rPr>
+      <t>https://www.arrowhead.eu/arrowheadtools</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <i/>
+        <color rgb="FF000000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t xml:space="preserve"> not accessible</t>
+    </r>
+  </si>
+  <si>
+    <t>Related Challenge - See SPE paper (Write Others in comment cell)</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>Intelligence and automation</t>
+  </si>
+  <si>
+    <t>Continuous software and system engineering</t>
+  </si>
+  <si>
     <t>n.a.</t>
   </si>
   <si>
-    <t>&lt;add your comment here if any&gt;</t>
-  </si>
-  <si>
-    <t>SECO Tools Availability (add repository or website in the comment)</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Several platforms/tools/standards/soution alternatives, IoT platforms in the cloud (e.g., Ayla or Cumulocity), </t>
-  </si>
-  <si>
-    <t>Related Challenge - See SPE paper (Write Others in comment cell)</t>
-  </si>
-  <si>
-    <t>Data</t>
-  </si>
-  <si>
-    <t>Intelligence and automation</t>
-  </si>
-  <si>
-    <t>Integration, security</t>
+    <t>Servitization: the process of creating value in products by adding services</t>
   </si>
   <si>
     <t>Does it contribute to answer RQ1?</t>
   </si>
   <si>
-    <t>A lot of talk about buisness, value chain, new personell, new roles, bridging silos, etc.</t>
+    <t>Interoperability, Software and Hardware Engineering, Determine relevant data, Difficulties for adding new equipment (scalability)</t>
   </si>
   <si>
     <t>Does the paper present methods, tools, and benefits in terms of industry/academia collaboration? If so, write what methods, tools, and benefits in the comment column</t>
   </si>
   <si>
-    <t>The paper presents different organization working on the integration of software ecosystems. It presents the German industrial associations that defines a framework (i.e., Reference Architecture Modell Industry 4.0 - RAMI 4.0) in Industry 4.0, the industrial data space (IDS) initiative and its reference architecture, and the Industrial internet consortium (IIC) and the W3C web of things interest group, with the WebOfThings interaction model. finally, it presents the Hadoop ecosystem, with the open source Apache Hadoop software library is the most prominent open source framework that allows for the distributed processing of large, structured and unstructured datasets across clusters of computers. DATA: The Hadoop ecosystem is gradually turning into a general-purpose data-operating system and is the leading framework for dealing with an extraordinary influx of datasets, often with a need to compute in real-time.</t>
+    <t>improving machine tool performance and optimizing manufacturing resources, to develop smart services on top of CPS, integrate third party applications, make production more efficient and predictable</t>
   </si>
   <si>
     <t>Does it contribute to answer RQ2?</t>
   </si>
   <si>
-    <t>More related to DATA.</t>
+    <t>Partially</t>
+  </si>
+  <si>
+    <t>A company provides engineering services along electronic product development life cycle focusing in the development of sensors and CPS and a university provides interoperability platforms.</t>
   </si>
   <si>
     <t>Application Domain(s) (at least one or domain independent)</t>
   </si>
   <si>
-    <t>Application Domain Independent</t>
-  </si>
-  <si>
-    <t>Industry 4.0, cloud</t>
+    <t>Manufacturing</t>
+  </si>
+  <si>
+    <t>Machine Tooling ecosystem: integration of grinding machines with other sensors, components or machines</t>
   </si>
   <si>
     <t>Quality Evaluation (From 1 to 10) - From "Quality" Tab</t>
@@ -215,7 +243,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -241,6 +269,13 @@
       <name val="Arial"/>
     </font>
     <font/>
+    <font>
+      <i/>
+      <u/>
+      <sz val="10.0"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+    </font>
     <font>
       <sz val="12.0"/>
       <color theme="1"/>
@@ -467,11 +502,13 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF000000"/>
       </right>
-      <top/>
-      <bottom style="thin">
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="double">
         <color rgb="FF000000"/>
       </bottom>
     </border>
@@ -479,13 +516,11 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
     </border>
@@ -598,7 +633,7 @@
     <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="8" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="9" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="10" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="11" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -611,19 +646,16 @@
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
     <xf borderId="16" fillId="4" fontId="1" numFmtId="1" xfId="0" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="15" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="17" fillId="5" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="17" fillId="5" fontId="5" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="18" fillId="5" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="18" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="16" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="18" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="17" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="19" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -636,93 +668,96 @@
     <xf borderId="19" fillId="5" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
+    <xf borderId="17" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
     <xf borderId="21" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
     <xf borderId="21" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="18" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="17" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="18" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="17" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="22" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="22" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="23" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="23" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="24" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf borderId="25" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="24" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf borderId="25" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="25" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="24" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="25" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="26" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="24" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="24" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="26" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="25" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="24" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="24" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="24" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf borderId="25" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="25" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="25" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="24" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="24" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf borderId="25" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="25" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="25" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -973,7 +1008,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="2.5"/>
-    <col customWidth="1" min="2" max="2" width="46.13"/>
+    <col customWidth="1" min="2" max="2" width="62.38"/>
     <col customWidth="1" min="3" max="3" width="9.0"/>
     <col customWidth="1" min="4" max="4" width="9.88"/>
     <col customWidth="1" min="5" max="5" width="9.0"/>
@@ -1020,7 +1055,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="243.0" customHeight="1">
+    <row r="3" ht="82.5" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="11"/>
       <c r="C3" s="12"/>
@@ -1038,8 +1073,8 @@
       <c r="B4" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="17" t="s">
-        <v>7</v>
+      <c r="C4" s="17">
+        <v>1.0</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18"/>
@@ -1047,7 +1082,7 @@
       <c r="G4" s="18"/>
       <c r="H4" s="18"/>
       <c r="I4" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
@@ -1055,18 +1090,18 @@
         <v>3.0</v>
       </c>
       <c r="B5" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="20" t="s">
         <v>9</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>10</v>
       </c>
       <c r="D5" s="18"/>
       <c r="E5" s="18"/>
       <c r="F5" s="18"/>
       <c r="G5" s="18"/>
       <c r="H5" s="18"/>
-      <c r="I5" s="21" t="s">
-        <v>11</v>
+      <c r="I5" s="19" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -1074,66 +1109,66 @@
         <v>4.0</v>
       </c>
       <c r="B6" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="D6" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="E6" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="H6" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="I6" s="23" t="s">
+      <c r="F6" s="21" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7">
+      <c r="G6" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="22" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="16">
         <v>5.0</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
+        <v>17</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
       <c r="H7" s="18"/>
-      <c r="I7" s="23" t="s">
-        <v>17</v>
+      <c r="I7" s="22" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="16">
         <v>6.0</v>
       </c>
-      <c r="B8" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
+      <c r="B8" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
       <c r="H8" s="18"/>
-      <c r="I8" s="23" t="s">
-        <v>19</v>
+      <c r="I8" s="22" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -1141,18 +1176,18 @@
         <v>7.0</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
+        <v>21</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
       <c r="H9" s="18"/>
-      <c r="I9" s="21" t="s">
-        <v>21</v>
+      <c r="I9" s="27" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -1160,28 +1195,28 @@
         <v>8.0</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E10" s="29" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F10" s="29" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H10" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="I10" s="23" t="s">
-        <v>24</v>
+        <v>15</v>
+      </c>
+      <c r="I10" s="22" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -1189,30 +1224,30 @@
         <v>9.0</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C11" s="30">
         <f>Quality!C29</f>
-        <v>3.888888889</v>
-      </c>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
+        <v>7.592592593</v>
+      </c>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
       <c r="I11" s="31" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1"/>
     <row r="14" ht="15.75" customHeight="1">
       <c r="B14" s="32" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="B15" s="32" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1"/>
@@ -2249,10 +2284,14 @@
       <formula1>"n.a.,Y,N"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="I4"/>
+    <hyperlink r:id="rId2" ref="I5"/>
+  </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -2273,10 +2312,10 @@
     <row r="1">
       <c r="A1" s="33"/>
       <c r="B1" s="34" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C1" s="34" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D1" s="35"/>
       <c r="E1" s="36"/>
@@ -2284,10 +2323,10 @@
     </row>
     <row r="2">
       <c r="A2" s="38" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B2" s="39" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" s="40">
         <v>1.0</v>
@@ -2299,7 +2338,7 @@
     <row r="3">
       <c r="A3" s="42"/>
       <c r="B3" s="39" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" s="40">
         <v>1.0</v>
@@ -2311,10 +2350,10 @@
     <row r="4">
       <c r="A4" s="42"/>
       <c r="B4" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="43">
-        <v>0.5</v>
+        <v>35</v>
+      </c>
+      <c r="C4" s="40">
+        <v>1.0</v>
       </c>
       <c r="D4" s="35"/>
       <c r="E4" s="35"/>
@@ -2322,10 +2361,10 @@
     <row r="5">
       <c r="A5" s="42"/>
       <c r="B5" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="43">
-        <v>0.5</v>
+        <v>36</v>
+      </c>
+      <c r="C5" s="40">
+        <v>1.0</v>
       </c>
       <c r="D5" s="35"/>
       <c r="E5" s="35"/>
@@ -2333,20 +2372,20 @@
     <row r="6">
       <c r="A6" s="42"/>
       <c r="B6" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="43">
-        <v>0.5</v>
+        <v>37</v>
+      </c>
+      <c r="C6" s="40">
+        <v>1.0</v>
       </c>
       <c r="D6" s="35"/>
       <c r="E6" s="35"/>
     </row>
     <row r="7">
-      <c r="A7" s="44"/>
+      <c r="A7" s="43"/>
       <c r="B7" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="43">
+        <v>38</v>
+      </c>
+      <c r="C7" s="44">
         <v>0.5</v>
       </c>
       <c r="D7" s="45">
@@ -2355,18 +2394,18 @@
       </c>
       <c r="E7" s="45">
         <f>(SUM(C2:C7)/D7)*10</f>
-        <v>6.666666667</v>
+        <v>9.166666667</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="46" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C8" s="48">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
       <c r="D8" s="35"/>
       <c r="E8" s="35"/>
@@ -2374,10 +2413,10 @@
     <row r="9">
       <c r="A9" s="42"/>
       <c r="B9" s="47" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C9" s="48">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
       <c r="D9" s="35"/>
       <c r="E9" s="35"/>
@@ -2385,10 +2424,10 @@
     <row r="10">
       <c r="A10" s="42"/>
       <c r="B10" s="47" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C10" s="48">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
       <c r="D10" s="35"/>
       <c r="E10" s="35"/>
@@ -2396,7 +2435,7 @@
     <row r="11">
       <c r="A11" s="42"/>
       <c r="B11" s="47" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C11" s="48">
         <v>0.0</v>
@@ -2407,7 +2446,7 @@
     <row r="12">
       <c r="A12" s="42"/>
       <c r="B12" s="47" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C12" s="48">
         <v>0.5</v>
@@ -2418,10 +2457,10 @@
     <row r="13">
       <c r="A13" s="42"/>
       <c r="B13" s="47" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" s="48">
-        <v>0.5</v>
+        <v>45</v>
+      </c>
+      <c r="C13" s="49">
+        <v>1.0</v>
       </c>
       <c r="D13" s="35"/>
       <c r="E13" s="35"/>
@@ -2429,10 +2468,10 @@
     <row r="14">
       <c r="A14" s="42"/>
       <c r="B14" s="47" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="48">
-        <v>0.5</v>
+        <v>46</v>
+      </c>
+      <c r="C14" s="49">
+        <v>1.0</v>
       </c>
       <c r="D14" s="35"/>
       <c r="E14" s="35"/>
@@ -2440,10 +2479,10 @@
     <row r="15">
       <c r="A15" s="42"/>
       <c r="B15" s="47" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C15" s="48">
-        <v>0.5</v>
+        <v>0.0</v>
       </c>
       <c r="D15" s="35"/>
       <c r="E15" s="35"/>
@@ -2451,7 +2490,7 @@
     <row r="16">
       <c r="A16" s="42"/>
       <c r="B16" s="47" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C16" s="48">
         <v>0.0</v>
@@ -2462,10 +2501,10 @@
     <row r="17">
       <c r="A17" s="42"/>
       <c r="B17" s="47" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" s="48">
-        <v>0.0</v>
+        <v>49</v>
+      </c>
+      <c r="C17" s="49">
+        <v>1.0</v>
       </c>
       <c r="D17" s="35"/>
       <c r="E17" s="35"/>
@@ -2473,7 +2512,7 @@
     <row r="18">
       <c r="A18" s="42"/>
       <c r="B18" s="47" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C18" s="49">
         <v>1.0</v>
@@ -2482,12 +2521,12 @@
       <c r="E18" s="35"/>
     </row>
     <row r="19">
-      <c r="A19" s="44"/>
+      <c r="A19" s="43"/>
       <c r="B19" s="47" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C19" s="48">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
       <c r="D19" s="45">
         <f>COUNTIF(B8:B19,"&lt;&gt;text")</f>
@@ -2495,18 +2534,18 @@
       </c>
       <c r="E19" s="45">
         <f>(SUM(C8:C19)/D19)*10</f>
-        <v>2.5</v>
+        <v>5.416666667</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="50" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B20" s="51" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C20" s="52">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="D20" s="35"/>
       <c r="E20" s="35"/>
@@ -2514,10 +2553,10 @@
     <row r="21">
       <c r="A21" s="42"/>
       <c r="B21" s="51" t="s">
-        <v>52</v>
-      </c>
-      <c r="C21" s="52">
-        <v>0.0</v>
+        <v>54</v>
+      </c>
+      <c r="C21" s="53">
+        <v>0.5</v>
       </c>
       <c r="D21" s="35"/>
       <c r="E21" s="35"/>
@@ -2525,10 +2564,10 @@
     <row r="22">
       <c r="A22" s="42"/>
       <c r="B22" s="51" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C22" s="52">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="D22" s="35"/>
       <c r="E22" s="35"/>
@@ -2536,10 +2575,10 @@
     <row r="23">
       <c r="A23" s="42"/>
       <c r="B23" s="51" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C23" s="52">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D23" s="36"/>
       <c r="E23" s="36"/>
@@ -2548,41 +2587,41 @@
     <row r="24">
       <c r="A24" s="42"/>
       <c r="B24" s="51" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C24" s="52">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="D24" s="36"/>
       <c r="E24" s="36"/>
       <c r="F24" s="41"/>
     </row>
     <row r="25">
-      <c r="A25" s="44"/>
+      <c r="A25" s="43"/>
       <c r="B25" s="51" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C25" s="52">
-        <v>0.5</v>
-      </c>
-      <c r="D25" s="53">
+        <v>1.0</v>
+      </c>
+      <c r="D25" s="54">
         <f>COUNTIF(B20:B25,"&lt;&gt;text")</f>
         <v>6</v>
       </c>
-      <c r="E25" s="53">
+      <c r="E25" s="54">
         <f>(SUM(C20:C25)/D25)*10</f>
-        <v>3.333333333</v>
+        <v>9.166666667</v>
       </c>
       <c r="F25" s="41"/>
     </row>
     <row r="26">
-      <c r="A26" s="54" t="s">
-        <v>57</v>
-      </c>
-      <c r="B26" s="55" t="s">
-        <v>58</v>
-      </c>
-      <c r="C26" s="56">
+      <c r="A26" s="55" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="56" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" s="57">
         <v>1.0</v>
       </c>
       <c r="D26" s="36"/>
@@ -2591,31 +2630,31 @@
     </row>
     <row r="27">
       <c r="A27" s="42"/>
-      <c r="B27" s="55" t="s">
-        <v>59</v>
+      <c r="B27" s="56" t="s">
+        <v>61</v>
       </c>
       <c r="C27" s="57">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="D27" s="36"/>
       <c r="E27" s="36"/>
       <c r="F27" s="41"/>
     </row>
     <row r="28">
-      <c r="A28" s="44"/>
-      <c r="B28" s="55" t="s">
-        <v>60</v>
+      <c r="A28" s="43"/>
+      <c r="B28" s="56" t="s">
+        <v>62</v>
       </c>
       <c r="C28" s="57">
-        <v>0.0</v>
-      </c>
-      <c r="D28" s="53">
+        <v>1.0</v>
+      </c>
+      <c r="D28" s="54">
         <f>COUNTIF(B26:B28,"&lt;&gt;text")</f>
         <v>3</v>
       </c>
-      <c r="E28" s="53">
+      <c r="E28" s="54">
         <f>(SUM(C26:C28)/D28)*10</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F28" s="41"/>
     </row>
@@ -2626,7 +2665,7 @@
       </c>
       <c r="C29" s="58">
         <f>(SUM(C2:C28)/B29)*10</f>
-        <v>3.888888889</v>
+        <v>7.592592593</v>
       </c>
     </row>
   </sheetData>
